--- a/artfynd/A 61182-2023 artfynd.xlsx
+++ b/artfynd/A 61182-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61182-2023 artfynd.xlsx
+++ b/artfynd/A 61182-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5095,10 +5095,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>116521868</v>
+        <v>116521873</v>
       </c>
       <c r="B39" t="n">
-        <v>79642</v>
+        <v>90426</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5107,25 +5107,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>346012</v>
+        <v>345975</v>
       </c>
       <c r="R39" t="n">
-        <v>6523624</v>
+        <v>6523646</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5197,10 +5197,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>116521873</v>
+        <v>116521878</v>
       </c>
       <c r="B40" t="n">
-        <v>90426</v>
+        <v>5185</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5213,34 +5213,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4660</v>
+        <v>105930</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sågeviken, Dls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>345975</v>
+        <v>345916</v>
       </c>
       <c r="R40" t="n">
-        <v>6523646</v>
+        <v>6523667</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5281,8 +5290,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5299,10 +5324,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>116521878</v>
+        <v>116521860</v>
       </c>
       <c r="B41" t="n">
-        <v>5185</v>
+        <v>100026</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5315,43 +5340,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sågeviken, Dls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>345916</v>
+        <v>346082</v>
       </c>
       <c r="R41" t="n">
-        <v>6523667</v>
+        <v>6523748</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5392,24 +5408,8 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5426,10 +5426,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>116521860</v>
+        <v>116521828</v>
       </c>
       <c r="B42" t="n">
-        <v>100026</v>
+        <v>90407</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5442,21 +5442,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5466,10 +5466,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>346082</v>
+        <v>345998</v>
       </c>
       <c r="R42" t="n">
-        <v>6523748</v>
+        <v>6523545</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5512,6 +5512,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5528,10 +5543,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>116521828</v>
+        <v>116521822</v>
       </c>
       <c r="B43" t="n">
-        <v>90407</v>
+        <v>74613</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5544,21 +5559,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5568,10 +5583,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>345998</v>
+        <v>346078</v>
       </c>
       <c r="R43" t="n">
-        <v>6523545</v>
+        <v>6523506</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5614,21 +5629,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5645,10 +5645,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>116521822</v>
+        <v>116521833</v>
       </c>
       <c r="B44" t="n">
-        <v>74613</v>
+        <v>90426</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5661,21 +5661,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>4660</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5685,10 +5685,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>346078</v>
+        <v>345989</v>
       </c>
       <c r="R44" t="n">
-        <v>6523506</v>
+        <v>6523701</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5731,6 +5731,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5747,10 +5762,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>116521833</v>
+        <v>116521857</v>
       </c>
       <c r="B45" t="n">
-        <v>90426</v>
+        <v>90453</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5763,21 +5778,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4660</v>
+        <v>1205</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5787,10 +5802,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>345989</v>
+        <v>346121</v>
       </c>
       <c r="R45" t="n">
-        <v>6523701</v>
+        <v>6523675</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5864,10 +5879,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>116521857</v>
+        <v>116521870</v>
       </c>
       <c r="B46" t="n">
-        <v>90453</v>
+        <v>74613</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5880,21 +5895,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1205</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5904,10 +5919,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>346121</v>
+        <v>345994</v>
       </c>
       <c r="R46" t="n">
-        <v>6523675</v>
+        <v>6523636</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5950,21 +5965,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5981,7 +5981,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>116521870</v>
+        <v>116521826</v>
       </c>
       <c r="B47" t="n">
         <v>74613</v>
@@ -6021,10 +6021,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>345994</v>
+        <v>346033</v>
       </c>
       <c r="R47" t="n">
-        <v>6523636</v>
+        <v>6523550</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6083,10 +6083,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>116521826</v>
+        <v>116521820</v>
       </c>
       <c r="B48" t="n">
-        <v>74613</v>
+        <v>5185</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6099,34 +6099,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sågeviken, Dls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>346033</v>
+        <v>346062</v>
       </c>
       <c r="R48" t="n">
-        <v>6523550</v>
+        <v>6523489</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6169,6 +6174,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6185,10 +6205,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>116521820</v>
+        <v>116521865</v>
       </c>
       <c r="B49" t="n">
-        <v>5185</v>
+        <v>79642</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6197,43 +6217,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sågeviken, Dls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>346062</v>
+        <v>346022</v>
       </c>
       <c r="R49" t="n">
-        <v>6523489</v>
+        <v>6523633</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6276,21 +6291,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6307,7 +6307,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>116521865</v>
+        <v>116521861</v>
       </c>
       <c r="B50" t="n">
         <v>79642</v>
@@ -6347,10 +6347,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>346022</v>
+        <v>346031</v>
       </c>
       <c r="R50" t="n">
-        <v>6523633</v>
+        <v>6523685</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6409,10 +6409,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>116521861</v>
+        <v>116521869</v>
       </c>
       <c r="B51" t="n">
-        <v>79642</v>
+        <v>79602</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6421,25 +6421,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>346031</v>
+        <v>345998</v>
       </c>
       <c r="R51" t="n">
-        <v>6523685</v>
+        <v>6523636</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6495,6 +6495,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6511,10 +6526,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>116521869</v>
+        <v>116521852</v>
       </c>
       <c r="B52" t="n">
-        <v>79602</v>
+        <v>90453</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6527,21 +6542,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>1205</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6551,10 +6566,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>345998</v>
+        <v>346173</v>
       </c>
       <c r="R52" t="n">
-        <v>6523636</v>
+        <v>6523653</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6597,21 +6612,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6628,10 +6628,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>116521852</v>
+        <v>116521872</v>
       </c>
       <c r="B53" t="n">
-        <v>90453</v>
+        <v>94272</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6644,21 +6644,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1205</v>
+        <v>2667</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>346173</v>
+        <v>345978</v>
       </c>
       <c r="R53" t="n">
-        <v>6523653</v>
+        <v>6523642</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6714,6 +6714,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6730,10 +6745,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>116521872</v>
+        <v>116521831</v>
       </c>
       <c r="B54" t="n">
-        <v>94272</v>
+        <v>79642</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6742,25 +6757,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2667</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6770,10 +6785,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>345978</v>
+        <v>345985</v>
       </c>
       <c r="R54" t="n">
-        <v>6523642</v>
+        <v>6523689</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6819,17 +6834,17 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6847,7 +6862,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>116521831</v>
+        <v>116521864</v>
       </c>
       <c r="B55" t="n">
         <v>79642</v>
@@ -6887,10 +6902,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>345985</v>
+        <v>346026</v>
       </c>
       <c r="R55" t="n">
-        <v>6523689</v>
+        <v>6523635</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6933,21 +6948,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6964,10 +6964,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>116521864</v>
+        <v>116521827</v>
       </c>
       <c r="B56" t="n">
-        <v>79642</v>
+        <v>74613</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6976,25 +6976,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>346026</v>
+        <v>346008</v>
       </c>
       <c r="R56" t="n">
-        <v>6523635</v>
+        <v>6523530</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7066,10 +7066,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>116521827</v>
+        <v>116521832</v>
       </c>
       <c r="B57" t="n">
-        <v>74613</v>
+        <v>79642</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7078,25 +7078,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>346008</v>
+        <v>345989</v>
       </c>
       <c r="R57" t="n">
-        <v>6523530</v>
+        <v>6523701</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7168,10 +7168,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>116521832</v>
+        <v>116521874</v>
       </c>
       <c r="B58" t="n">
-        <v>79642</v>
+        <v>100026</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7180,25 +7180,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7208,10 +7208,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>345989</v>
+        <v>345970</v>
       </c>
       <c r="R58" t="n">
-        <v>6523701</v>
+        <v>6523665</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7270,7 +7270,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>116521874</v>
+        <v>116521877</v>
       </c>
       <c r="B59" t="n">
         <v>100026</v>
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>345970</v>
+        <v>345958</v>
       </c>
       <c r="R59" t="n">
-        <v>6523665</v>
+        <v>6523686</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7372,10 +7372,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>116521877</v>
+        <v>116521862</v>
       </c>
       <c r="B60" t="n">
-        <v>100026</v>
+        <v>79642</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7384,25 +7384,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>345958</v>
+        <v>346020</v>
       </c>
       <c r="R60" t="n">
-        <v>6523686</v>
+        <v>6523671</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7458,6 +7458,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7474,10 +7489,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>116521862</v>
+        <v>116521867</v>
       </c>
       <c r="B61" t="n">
-        <v>79642</v>
+        <v>100026</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7486,25 +7501,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7514,10 +7529,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>346020</v>
+        <v>346017</v>
       </c>
       <c r="R61" t="n">
-        <v>6523671</v>
+        <v>6523623</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7560,21 +7575,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7591,10 +7591,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>116521867</v>
+        <v>116521876</v>
       </c>
       <c r="B62" t="n">
-        <v>100026</v>
+        <v>90850</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7607,21 +7607,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>5321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rigidoporus corticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>346017</v>
+        <v>345973</v>
       </c>
       <c r="R62" t="n">
-        <v>6523623</v>
+        <v>6523677</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7675,8 +7675,24 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7693,10 +7709,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>116521876</v>
+        <v>116521836</v>
       </c>
       <c r="B63" t="n">
-        <v>90850</v>
+        <v>74613</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7709,21 +7725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5321</v>
+        <v>6426</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7733,10 +7749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>345973</v>
+        <v>345974</v>
       </c>
       <c r="R63" t="n">
-        <v>6523677</v>
+        <v>6523874</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7777,24 +7793,8 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7811,10 +7811,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>116521836</v>
+        <v>116521881</v>
       </c>
       <c r="B64" t="n">
-        <v>74613</v>
+        <v>79602</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7827,34 +7827,41 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sågeviken, Dls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>345974</v>
+        <v>345903</v>
       </c>
       <c r="R64" t="n">
-        <v>6523874</v>
+        <v>6523627</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7895,8 +7902,24 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7913,10 +7936,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>116521881</v>
+        <v>116521858</v>
       </c>
       <c r="B65" t="n">
-        <v>79602</v>
+        <v>74613</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7929,41 +7952,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sågeviken, Dls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>345903</v>
+        <v>346134</v>
       </c>
       <c r="R65" t="n">
-        <v>6523627</v>
+        <v>6523744</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8004,23 +8020,22 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8038,10 +8053,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>116521858</v>
+        <v>116884817</v>
       </c>
       <c r="B66" t="n">
-        <v>74613</v>
+        <v>94303</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8054,21 +8069,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8078,10 +8093,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>346134</v>
+        <v>346112</v>
       </c>
       <c r="R66" t="n">
-        <v>6523744</v>
+        <v>6523762</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8152,123 +8167,6 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>116884817</v>
-      </c>
-      <c r="B67" t="n">
-        <v>94303</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>2818</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Stubbspretmossa</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Herzogiella seligeri</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Sågeviken, Dls</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>346112</v>
-      </c>
-      <c r="R67" t="n">
-        <v>6523762</v>
-      </c>
-      <c r="S67" t="n">
-        <v>5</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Mellerud</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Dalsland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Dalskog</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
